--- a/artfynd/A 17637-2024 artfynd.xlsx
+++ b/artfynd/A 17637-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658576</v>
+        <v>117658573</v>
       </c>
       <c r="B2" t="n">
-        <v>86816</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420037</v>
+        <v>419417</v>
       </c>
       <c r="R2" t="n">
-        <v>7050284</v>
+        <v>7050601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658573</v>
+        <v>117658576</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>86816</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419417</v>
+        <v>420037</v>
       </c>
       <c r="R4" t="n">
-        <v>7050601</v>
+        <v>7050284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 17637-2024 artfynd.xlsx
+++ b/artfynd/A 17637-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658573</v>
+        <v>117658574</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419417</v>
+        <v>419406</v>
       </c>
       <c r="R2" t="n">
-        <v>7050601</v>
+        <v>7050608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658574</v>
+        <v>117658576</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>86818</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419406</v>
+        <v>420037</v>
       </c>
       <c r="R3" t="n">
-        <v>7050608</v>
+        <v>7050284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658576</v>
+        <v>117658573</v>
       </c>
       <c r="B4" t="n">
-        <v>86816</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420037</v>
+        <v>419417</v>
       </c>
       <c r="R4" t="n">
-        <v>7050284</v>
+        <v>7050601</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
